--- a/tinHelm/excel/Enemy.xlsx
+++ b/tinHelm/excel/Enemy.xlsx
@@ -1133,7 +1133,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>5001</v>
+        <v>1</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
